--- a/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre_Final.xlsx
+++ b/pds_admin_Punjab_R/Backend/Backend/Tagging_Sheet_Pre_Final.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="86">
   <si>
     <t>Tagging</t>
   </si>
@@ -43,25 +43,235 @@
     <t>Values</t>
   </si>
   <si>
+    <t>X_1066_jalandharcity_33_vallah_Wheat	65710.0</t>
+  </si>
+  <si>
+    <t>X_10_amritsar_41_bhagtanwala_Wheat	60000.0</t>
+  </si>
+  <si>
+    <t>X_10_amritsar_42_bhagtanwala_Wheat	100000.0</t>
+  </si>
+  <si>
+    <t>X_10_amritsar_6_bhagtanwala_Wheat	70000.0</t>
+  </si>
+  <si>
+    <t>X_10_amritsar_7_bhagtanwala_Wheat	120000.0</t>
+  </si>
+  <si>
+    <t>X_10_amritsar_8_bhagtanwala_Wheat	35000.0</t>
+  </si>
+  <si>
+    <t>X_11_amritsar_22_verka_Wheat	19258.5</t>
+  </si>
+  <si>
+    <t>X_11_amritsar_24_chhehrata_Wheat	52445.5</t>
+  </si>
+  <si>
     <t>X_1660_malout_407_abohar_Wheat	15621.0</t>
   </si>
   <si>
+    <t>X_18_attari_24_chhehrata_Wheat	6721.0</t>
+  </si>
+  <si>
+    <t>X_18_attari_26_chhehrata_Wheat	80000.0</t>
+  </si>
+  <si>
+    <t>X_2139_naushehrapannuan_40_vallah_Wheat	91350.0</t>
+  </si>
+  <si>
+    <t>X_2151_tarntaran_40_vallah_Wheat	33650.0</t>
+  </si>
+  <si>
+    <t>X_2153_bhikhiwind_10_chhehrata_Wheat	60000.0</t>
+  </si>
+  <si>
+    <t>X_2153_bhikhiwind_4_verka_Wheat	150000.0</t>
+  </si>
+  <si>
+    <t>X_2153_bhikhiwind_9_bhagtanwala_Wheat	35000.0</t>
+  </si>
+  <si>
+    <t>X_21_attari_24_chhehrata_Wheat	833.5</t>
+  </si>
+  <si>
+    <t>X_21_attari_25_chhehrata_Wheat	80000.0</t>
+  </si>
+  <si>
+    <t>X_28_chogawan_22_verka_Wheat	107242.5</t>
+  </si>
+  <si>
+    <t>X_31_chogawan_22_verka_Wheat	3499.0</t>
+  </si>
+  <si>
+    <t>X_39_jandiala_32_chhehrata_Wheat	59553.0</t>
+  </si>
+  <si>
+    <t>X_49_mehta_32_chhehrata_Wheat	5447.0</t>
+  </si>
+  <si>
     <t>X</t>
   </si>
   <si>
+    <t>jalandharcity</t>
+  </si>
+  <si>
+    <t>amritsar</t>
+  </si>
+  <si>
     <t>malout</t>
   </si>
   <si>
+    <t>attari</t>
+  </si>
+  <si>
+    <t>naushehrapannuan</t>
+  </si>
+  <si>
+    <t>tarntaran</t>
+  </si>
+  <si>
+    <t>bhikhiwind</t>
+  </si>
+  <si>
+    <t>chogawan</t>
+  </si>
+  <si>
+    <t>jandiala</t>
+  </si>
+  <si>
+    <t>mehta</t>
+  </si>
+  <si>
+    <t>vallah</t>
+  </si>
+  <si>
+    <t>bhagtanwala</t>
+  </si>
+  <si>
+    <t>verka</t>
+  </si>
+  <si>
+    <t>chhehrata</t>
+  </si>
+  <si>
     <t>abohar</t>
   </si>
   <si>
+    <t>Wheat	65710.0</t>
+  </si>
+  <si>
+    <t>Wheat	60000.0</t>
+  </si>
+  <si>
+    <t>Wheat	100000.0</t>
+  </si>
+  <si>
+    <t>Wheat	70000.0</t>
+  </si>
+  <si>
+    <t>Wheat	120000.0</t>
+  </si>
+  <si>
+    <t>Wheat	35000.0</t>
+  </si>
+  <si>
+    <t>Wheat	19258.5</t>
+  </si>
+  <si>
+    <t>Wheat	52445.5</t>
+  </si>
+  <si>
     <t>Wheat	15621.0</t>
   </si>
   <si>
+    <t>Wheat	6721.0</t>
+  </si>
+  <si>
+    <t>Wheat	80000.0</t>
+  </si>
+  <si>
+    <t>Wheat	91350.0</t>
+  </si>
+  <si>
+    <t>Wheat	33650.0</t>
+  </si>
+  <si>
+    <t>Wheat	150000.0</t>
+  </si>
+  <si>
+    <t>Wheat	833.5</t>
+  </si>
+  <si>
+    <t>Wheat	107242.5</t>
+  </si>
+  <si>
+    <t>Wheat	3499.0</t>
+  </si>
+  <si>
+    <t>Wheat	59553.0</t>
+  </si>
+  <si>
+    <t>Wheat	5447.0</t>
+  </si>
+  <si>
     <t>Wheat</t>
   </si>
   <si>
+    <t>65710.0</t>
+  </si>
+  <si>
+    <t>60000.0</t>
+  </si>
+  <si>
+    <t>100000.0</t>
+  </si>
+  <si>
+    <t>70000.0</t>
+  </si>
+  <si>
+    <t>120000.0</t>
+  </si>
+  <si>
+    <t>35000.0</t>
+  </si>
+  <si>
+    <t>19258.5</t>
+  </si>
+  <si>
+    <t>52445.5</t>
+  </si>
+  <si>
     <t>15621.0</t>
+  </si>
+  <si>
+    <t>6721.0</t>
+  </si>
+  <si>
+    <t>80000.0</t>
+  </si>
+  <si>
+    <t>91350.0</t>
+  </si>
+  <si>
+    <t>33650.0</t>
+  </si>
+  <si>
+    <t>150000.0</t>
+  </si>
+  <si>
+    <t>833.5</t>
+  </si>
+  <si>
+    <t>107242.5</t>
+  </si>
+  <si>
+    <t>3499.0</t>
+  </si>
+  <si>
+    <t>59553.0</t>
+  </si>
+  <si>
+    <t>5447.0</t>
   </si>
 </sst>
 </file>
@@ -419,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -459,28 +669,700 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2">
+        <v>1066</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="C3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3">
+        <v>41</v>
+      </c>
+      <c r="G3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8">
+        <v>22</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+      <c r="J9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
         <v>1660</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>407</v>
+      </c>
+      <c r="G10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11">
+        <v>24</v>
+      </c>
+      <c r="G11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="F2">
-        <v>407</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13">
+        <v>2139</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>40</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="H2" t="s">
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>2151</v>
+      </c>
+      <c r="E14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14">
+        <v>40</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15">
+        <v>2153</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16">
+        <v>2153</v>
+      </c>
+      <c r="E16" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="1">
         <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>2153</v>
+      </c>
+      <c r="E17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" t="s">
+        <v>52</v>
+      </c>
+      <c r="I17" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18">
+        <v>24</v>
+      </c>
+      <c r="G18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>21</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19">
+        <v>25</v>
+      </c>
+      <c r="G19" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" t="s">
+        <v>57</v>
+      </c>
+      <c r="I19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="1">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20">
+        <v>22</v>
+      </c>
+      <c r="G20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" t="s">
+        <v>62</v>
+      </c>
+      <c r="I20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+      <c r="E21" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21">
+        <v>22</v>
+      </c>
+      <c r="G21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" t="s">
+        <v>63</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
+      </c>
+      <c r="J21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="1">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22">
+        <v>39</v>
+      </c>
+      <c r="E22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>49</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>45</v>
+      </c>
+      <c r="H23" t="s">
+        <v>65</v>
+      </c>
+      <c r="I23" t="s">
+        <v>66</v>
+      </c>
+      <c r="J23" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
